--- a/data/analysis_ministral_3_14b_panns/multimodal_event_eval_ministral_3_14b_panns_w2_5s_h2_5s.xlsx
+++ b/data/analysis_ministral_3_14b_panns/multimodal_event_eval_ministral_3_14b_panns_w2_5s_h2_5s.xlsx
@@ -121,7 +121,7 @@
     <t>sound: engine(0-60), sound: engine(180-240), sound: gunshot_or_explosion(120-180), visual: carrying(144-216), visual: enter_or_exit_vehicle(48-48), visual: enter_or_exit_vehicle(96-96), visual: enter_or_exit_vehicle(96-96), visual: explosion_visible(120-120), visual: gunshot_visible(120-120), visual: running(144-144), visual: running(120-120), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(144-168), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(168-216), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(96-96)</t>
   </si>
   <si>
-    <t>sound: gunshot_or_explosion(0-60), sound: engine(60-240), visual: explosion_visible(24-240), visual: running(24-240), visual: running(120-240)</t>
+    <t>sound: gunshot_or_explosion(0-60), sound: engine(60-120), sound: engine(180-240), visual: explosion_visible(24-240), visual: running(24-240), visual: running(120-240)</t>
   </si>
   <si>
     <t>sound: gunshot_or_explosion(0-60), sound: engine(120-240), visual: enter_or_exit_vehicle(0-0), visual: explosion_visible(72-72), visual: explosion_visible(144-240), visual: explosion_visible(216-240), visual: explosion_visible(72-72), visual: explosion_visible(216-240), visual: explosion_visible(48-216), visual: explosion_visible(168-168), visual: running(96-240), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(0-24), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(216-240), visual: vehicle_collision(48-240), visual: vehicle_collision(48-48), visual: vehicle_collision(192-240), visual: vehicle_collision(72-120), visual: vehicle_collision(216-240)</t>
